--- a/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
@@ -61,7 +61,7 @@
     <t>Исполнитель</t>
   </si>
   <si>
-    <t xml:space="preserve">Индивидуальный предприниматель "XANSHA" Рыспаева Гаухар Сериковна                                                                                 РК, область Улытау, п.Жанаарка, ул.Сарыарка  д 6  кв 1, Жанааркинский район  </t>
+    <t xml:space="preserve">Индивидуальный предприниматель "XANSHA" Рыспаева Гаухар Сериковна                                                                                 РК, область Улытау, п.Жанаарка, ул.{documentAddress}, Жанааркинский район  </t>
   </si>
   <si>
     <t xml:space="preserve">полное наименование, адрес, данные о средствах связи</t>
